--- a/项目代码/EdgeMI/time_cost/分布式系统参数.xlsx
+++ b/项目代码/EdgeMI/time_cost/分布式系统参数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Graduate\EdgeLD\项目代码\EdgeMI\time_cost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85456E5B-75AC-468B-B395-EB16D219F5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07C3C89-2424-43FB-B4B9-753128A94D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2810" yWindow="1110" windowWidth="19290" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="111">
   <si>
     <t>Block1</t>
   </si>
@@ -413,6 +413,14 @@
   </si>
   <si>
     <t>主节点合并</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>切割 MaxPooling</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>VGG16 Block3-5 多节点&gt;=3</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -699,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,6 +857,21 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -863,14 +886,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -889,13 +904,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1178,83 +1194,83 @@
       <c r="A1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="79" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="79" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="79" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="79" t="s">
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
     </row>
     <row r="2" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="71"/>
+      <c r="B2" s="68"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="69"/>
+      <c r="E2" s="67"/>
       <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="71"/>
+      <c r="G2" s="68"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="69"/>
+      <c r="J2" s="67"/>
       <c r="K2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="71"/>
+      <c r="L2" s="68"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="69"/>
+      <c r="O2" s="67"/>
       <c r="P2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="71"/>
+      <c r="Q2" s="68"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="69"/>
+      <c r="T2" s="67"/>
       <c r="U2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="71"/>
+      <c r="V2" s="68"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="69"/>
+      <c r="Y2" s="67"/>
       <c r="Z2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1275,50 +1291,50 @@
       <c r="A3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="72"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="70"/>
+      <c r="E3" s="64"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="72"/>
+      <c r="G3" s="69"/>
       <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="70"/>
+      <c r="J3" s="64"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="72"/>
+      <c r="L3" s="69"/>
       <c r="M3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="70"/>
+      <c r="O3" s="64"/>
       <c r="P3" s="6"/>
-      <c r="Q3" s="72"/>
+      <c r="Q3" s="69"/>
       <c r="R3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="70"/>
+      <c r="T3" s="64"/>
       <c r="U3" s="6"/>
-      <c r="V3" s="72"/>
+      <c r="V3" s="69"/>
       <c r="W3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="70"/>
+      <c r="Y3" s="64"/>
       <c r="Z3" s="6"/>
       <c r="AA3" s="10"/>
       <c r="AB3" s="5"/>
@@ -1512,11 +1528,11 @@
       <c r="Z7" s="32">
         <v>1775024872.858</v>
       </c>
-      <c r="AA7" s="73">
+      <c r="AA7" s="76">
         <v>1775024872.938</v>
       </c>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="75"/>
+      <c r="AB7" s="77"/>
+      <c r="AC7" s="78"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
@@ -1573,11 +1589,11 @@
       <c r="Z8" s="34">
         <v>1775024872.869</v>
       </c>
-      <c r="AA8" s="76">
+      <c r="AA8" s="79">
         <v>1775024872.9489999</v>
       </c>
-      <c r="AB8" s="77"/>
-      <c r="AC8" s="78"/>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="81"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
@@ -1634,46 +1650,46 @@
       <c r="Z9" s="34">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="AA9" s="76">
+      <c r="AA9" s="79">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="AB9" s="77"/>
-      <c r="AC9" s="78"/>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="81"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="70"/>
-      <c r="Z10" s="70"/>
-      <c r="AA10" s="70"/>
-      <c r="AB10" s="70"/>
-      <c r="AC10" s="81"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
+      <c r="AA10" s="64"/>
+      <c r="AB10" s="64"/>
+      <c r="AC10" s="66"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
@@ -1735,36 +1751,36 @@
       <c r="A13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="66">
+      <c r="B13" s="73">
         <v>1000</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="67"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="67"/>
-      <c r="P13" s="67"/>
-      <c r="Q13" s="67"/>
-      <c r="R13" s="67"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="67"/>
-      <c r="U13" s="67"/>
-      <c r="V13" s="67"/>
-      <c r="W13" s="67"/>
-      <c r="X13" s="67"/>
-      <c r="Y13" s="67"/>
-      <c r="Z13" s="67"/>
-      <c r="AA13" s="67"/>
-      <c r="AB13" s="67"/>
-      <c r="AC13" s="68"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
+      <c r="T13" s="74"/>
+      <c r="U13" s="74"/>
+      <c r="V13" s="74"/>
+      <c r="W13" s="74"/>
+      <c r="X13" s="74"/>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="74"/>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="75"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
@@ -1819,35 +1835,35 @@
         <v>42</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="64"/>
-      <c r="U15" s="64"/>
-      <c r="V15" s="64"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="64"/>
-      <c r="Y15" s="64"/>
-      <c r="Z15" s="64"/>
-      <c r="AA15" s="64"/>
-      <c r="AB15" s="64"/>
-      <c r="AC15" s="65"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="72"/>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
@@ -2624,7 +2640,7 @@
       <c r="P80" s="45"/>
       <c r="Q80" s="45"/>
     </row>
-    <row r="81" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G81" s="45">
         <v>6</v>
       </c>
@@ -2638,7 +2654,7 @@
       <c r="P81" s="45"/>
       <c r="Q81" s="45"/>
     </row>
-    <row r="82" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G82" s="45">
         <v>7</v>
       </c>
@@ -2652,7 +2668,7 @@
       <c r="P82" s="45"/>
       <c r="Q82" s="45"/>
     </row>
-    <row r="83" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G83" s="45">
         <v>8</v>
       </c>
@@ -2666,7 +2682,7 @@
       <c r="P83" s="45"/>
       <c r="Q83" s="45"/>
     </row>
-    <row r="85" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G85" s="38" t="s">
         <v>95</v>
       </c>
@@ -2674,7 +2690,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G86" s="45">
         <v>1</v>
       </c>
@@ -2688,7 +2704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G87" s="45">
         <v>2</v>
       </c>
@@ -2698,7 +2714,7 @@
       </c>
       <c r="O87" s="45"/>
     </row>
-    <row r="88" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G88" s="45">
         <v>3</v>
       </c>
@@ -2708,7 +2724,7 @@
       </c>
       <c r="O88" s="45"/>
     </row>
-    <row r="89" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:32" x14ac:dyDescent="0.25">
       <c r="G89" s="45">
         <v>4</v>
       </c>
@@ -2718,7 +2734,7 @@
       </c>
       <c r="O89" s="45"/>
     </row>
-    <row r="90" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B90" s="59" t="s">
         <v>100</v>
       </c>
@@ -2726,7 +2742,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B91" s="57" t="s">
         <v>92</v>
       </c>
@@ -2749,8 +2765,17 @@
       <c r="P91" s="60" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="92" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W91" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y91" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z91" s="60" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B92" s="45">
         <v>1</v>
       </c>
@@ -2801,8 +2826,30 @@
       </c>
       <c r="T92" s="61"/>
       <c r="U92" s="61"/>
-    </row>
-    <row r="93" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W92" s="46">
+        <v>1</v>
+      </c>
+      <c r="X92" s="46">
+        <v>2</v>
+      </c>
+      <c r="Y92" s="46">
+        <v>3</v>
+      </c>
+      <c r="Z92" s="45">
+        <v>4</v>
+      </c>
+      <c r="AA92" s="45">
+        <v>5</v>
+      </c>
+      <c r="AB92" s="45">
+        <v>6</v>
+      </c>
+      <c r="AC92" s="82"/>
+      <c r="AD92" s="61"/>
+      <c r="AE92" s="83"/>
+      <c r="AF92" s="83"/>
+    </row>
+    <row r="93" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B93" s="45">
         <v>2</v>
       </c>
@@ -2827,8 +2874,20 @@
       <c r="S93" s="45"/>
       <c r="T93" s="61"/>
       <c r="U93" s="61"/>
-    </row>
-    <row r="94" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W93" s="46">
+        <v>2</v>
+      </c>
+      <c r="X93" s="46"/>
+      <c r="Y93" s="46"/>
+      <c r="Z93" s="45"/>
+      <c r="AA93" s="45"/>
+      <c r="AB93" s="45"/>
+      <c r="AC93" s="82"/>
+      <c r="AD93" s="61"/>
+      <c r="AE93" s="83"/>
+      <c r="AF93" s="83"/>
+    </row>
+    <row r="94" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B94" s="45">
         <v>3</v>
       </c>
@@ -2853,8 +2912,20 @@
       <c r="S94" s="45"/>
       <c r="T94" s="61"/>
       <c r="U94" s="61"/>
-    </row>
-    <row r="95" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W94" s="46">
+        <v>3</v>
+      </c>
+      <c r="X94" s="46"/>
+      <c r="Y94" s="46"/>
+      <c r="Z94" s="45"/>
+      <c r="AA94" s="45"/>
+      <c r="AB94" s="45"/>
+      <c r="AC94" s="82"/>
+      <c r="AD94" s="61"/>
+      <c r="AE94" s="83"/>
+      <c r="AF94" s="83"/>
+    </row>
+    <row r="95" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B95" s="45">
         <v>4</v>
       </c>
@@ -2879,8 +2950,20 @@
       <c r="S95" s="45"/>
       <c r="T95" s="61"/>
       <c r="U95" s="61"/>
-    </row>
-    <row r="96" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W95" s="46">
+        <v>4</v>
+      </c>
+      <c r="X95" s="46"/>
+      <c r="Y95" s="46"/>
+      <c r="Z95" s="45"/>
+      <c r="AA95" s="45"/>
+      <c r="AB95" s="45"/>
+      <c r="AC95" s="82"/>
+      <c r="AD95" s="61"/>
+      <c r="AE95" s="83"/>
+      <c r="AF95" s="83"/>
+    </row>
+    <row r="96" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B96" s="45">
         <v>5</v>
       </c>
@@ -2905,8 +2988,20 @@
       <c r="S96" s="45"/>
       <c r="T96" s="61"/>
       <c r="U96" s="61"/>
-    </row>
-    <row r="97" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W96" s="46">
+        <v>5</v>
+      </c>
+      <c r="X96" s="46"/>
+      <c r="Y96" s="46"/>
+      <c r="Z96" s="45"/>
+      <c r="AA96" s="45"/>
+      <c r="AB96" s="45"/>
+      <c r="AC96" s="82"/>
+      <c r="AD96" s="61"/>
+      <c r="AE96" s="83"/>
+      <c r="AF96" s="83"/>
+    </row>
+    <row r="97" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B97" s="45">
         <v>6</v>
       </c>
@@ -2931,8 +3026,20 @@
       <c r="S97" s="45"/>
       <c r="T97" s="61"/>
       <c r="U97" s="61"/>
-    </row>
-    <row r="98" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W97" s="46">
+        <v>6</v>
+      </c>
+      <c r="X97" s="46"/>
+      <c r="Y97" s="46"/>
+      <c r="Z97" s="45"/>
+      <c r="AA97" s="45"/>
+      <c r="AB97" s="45"/>
+      <c r="AC97" s="82"/>
+      <c r="AD97" s="61"/>
+      <c r="AE97" s="83"/>
+      <c r="AF97" s="83"/>
+    </row>
+    <row r="98" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B98" s="45">
         <v>7</v>
       </c>
@@ -2957,8 +3064,20 @@
       <c r="S98" s="45"/>
       <c r="T98" s="61"/>
       <c r="U98" s="61"/>
-    </row>
-    <row r="99" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W98" s="46">
+        <v>7</v>
+      </c>
+      <c r="X98" s="46"/>
+      <c r="Y98" s="46"/>
+      <c r="Z98" s="45"/>
+      <c r="AA98" s="45"/>
+      <c r="AB98" s="45"/>
+      <c r="AC98" s="82"/>
+      <c r="AD98" s="61"/>
+      <c r="AE98" s="83"/>
+      <c r="AF98" s="83"/>
+    </row>
+    <row r="99" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B99" s="45">
         <v>8</v>
       </c>
@@ -2983,8 +3102,20 @@
       <c r="S99" s="45"/>
       <c r="T99" s="61"/>
       <c r="U99" s="61"/>
-    </row>
-    <row r="101" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W99" s="46">
+        <v>8</v>
+      </c>
+      <c r="X99" s="46"/>
+      <c r="Y99" s="46"/>
+      <c r="Z99" s="45"/>
+      <c r="AA99" s="45"/>
+      <c r="AB99" s="45"/>
+      <c r="AC99" s="82"/>
+      <c r="AD99" s="61"/>
+      <c r="AE99" s="83"/>
+      <c r="AF99" s="83"/>
+    </row>
+    <row r="101" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B101" s="38" t="s">
         <v>87</v>
       </c>
@@ -2994,8 +3125,11 @@
       <c r="N101" s="38" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="102" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W101" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="102" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B102" s="45">
         <v>1</v>
       </c>
@@ -3040,8 +3174,30 @@
       </c>
       <c r="T102" s="47"/>
       <c r="U102" s="47"/>
-    </row>
-    <row r="103" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W102" s="47">
+        <v>1</v>
+      </c>
+      <c r="X102" s="47">
+        <v>2</v>
+      </c>
+      <c r="Y102" s="47">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="45">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="45">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="45">
+        <v>6</v>
+      </c>
+      <c r="AC102" s="82"/>
+      <c r="AD102" s="84"/>
+      <c r="AE102" s="85"/>
+      <c r="AF102" s="85"/>
+    </row>
+    <row r="103" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B103" s="45">
         <v>2</v>
       </c>
@@ -3066,8 +3222,20 @@
       <c r="S103" s="45"/>
       <c r="T103" s="47"/>
       <c r="U103" s="47"/>
-    </row>
-    <row r="104" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W103" s="47">
+        <v>2</v>
+      </c>
+      <c r="X103" s="47"/>
+      <c r="Y103" s="47"/>
+      <c r="Z103" s="45"/>
+      <c r="AA103" s="45"/>
+      <c r="AB103" s="45"/>
+      <c r="AC103" s="82"/>
+      <c r="AD103" s="84"/>
+      <c r="AE103" s="85"/>
+      <c r="AF103" s="85"/>
+    </row>
+    <row r="104" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B104" s="45">
         <v>3</v>
       </c>
@@ -3092,8 +3260,20 @@
       <c r="S104" s="45"/>
       <c r="T104" s="47"/>
       <c r="U104" s="47"/>
-    </row>
-    <row r="105" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W104" s="47">
+        <v>3</v>
+      </c>
+      <c r="X104" s="47"/>
+      <c r="Y104" s="47"/>
+      <c r="Z104" s="45"/>
+      <c r="AA104" s="45"/>
+      <c r="AB104" s="45"/>
+      <c r="AC104" s="82"/>
+      <c r="AD104" s="84"/>
+      <c r="AE104" s="85"/>
+      <c r="AF104" s="85"/>
+    </row>
+    <row r="105" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B105" s="45">
         <v>4</v>
       </c>
@@ -3118,8 +3298,20 @@
       <c r="S105" s="45"/>
       <c r="T105" s="47"/>
       <c r="U105" s="47"/>
-    </row>
-    <row r="106" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W105" s="47">
+        <v>4</v>
+      </c>
+      <c r="X105" s="47"/>
+      <c r="Y105" s="47"/>
+      <c r="Z105" s="45"/>
+      <c r="AA105" s="45"/>
+      <c r="AB105" s="45"/>
+      <c r="AC105" s="82"/>
+      <c r="AD105" s="84"/>
+      <c r="AE105" s="85"/>
+      <c r="AF105" s="85"/>
+    </row>
+    <row r="106" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B106" s="45"/>
       <c r="C106" s="45"/>
       <c r="D106" s="45"/>
@@ -3142,8 +3334,20 @@
       <c r="S106" s="45"/>
       <c r="T106" s="47"/>
       <c r="U106" s="47"/>
-    </row>
-    <row r="107" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W106" s="47">
+        <v>5</v>
+      </c>
+      <c r="X106" s="47"/>
+      <c r="Y106" s="47"/>
+      <c r="Z106" s="45"/>
+      <c r="AA106" s="45"/>
+      <c r="AB106" s="45"/>
+      <c r="AC106" s="82"/>
+      <c r="AD106" s="84"/>
+      <c r="AE106" s="85"/>
+      <c r="AF106" s="85"/>
+    </row>
+    <row r="107" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B107" s="45"/>
       <c r="C107" s="45"/>
       <c r="D107" s="45"/>
@@ -3166,8 +3370,20 @@
       <c r="S107" s="45"/>
       <c r="T107" s="47"/>
       <c r="U107" s="47"/>
-    </row>
-    <row r="108" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W107" s="47">
+        <v>6</v>
+      </c>
+      <c r="X107" s="47"/>
+      <c r="Y107" s="47"/>
+      <c r="Z107" s="45"/>
+      <c r="AA107" s="45"/>
+      <c r="AB107" s="45"/>
+      <c r="AC107" s="82"/>
+      <c r="AD107" s="84"/>
+      <c r="AE107" s="85"/>
+      <c r="AF107" s="85"/>
+    </row>
+    <row r="108" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B108" s="45"/>
       <c r="C108" s="45"/>
       <c r="D108" s="45"/>
@@ -3190,8 +3406,20 @@
       <c r="S108" s="45"/>
       <c r="T108" s="47"/>
       <c r="U108" s="47"/>
-    </row>
-    <row r="109" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W108" s="47">
+        <v>7</v>
+      </c>
+      <c r="X108" s="47"/>
+      <c r="Y108" s="47"/>
+      <c r="Z108" s="45"/>
+      <c r="AA108" s="45"/>
+      <c r="AB108" s="45"/>
+      <c r="AC108" s="82"/>
+      <c r="AD108" s="84"/>
+      <c r="AE108" s="85"/>
+      <c r="AF108" s="85"/>
+    </row>
+    <row r="109" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B109" s="45"/>
       <c r="C109" s="45"/>
       <c r="D109" s="45"/>
@@ -3214,8 +3442,20 @@
       <c r="S109" s="45"/>
       <c r="T109" s="47"/>
       <c r="U109" s="47"/>
-    </row>
-    <row r="111" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W109" s="47">
+        <v>8</v>
+      </c>
+      <c r="X109" s="47"/>
+      <c r="Y109" s="47"/>
+      <c r="Z109" s="45"/>
+      <c r="AA109" s="45"/>
+      <c r="AB109" s="45"/>
+      <c r="AC109" s="82"/>
+      <c r="AD109" s="84"/>
+      <c r="AE109" s="85"/>
+      <c r="AF109" s="85"/>
+    </row>
+    <row r="111" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B111" s="38" t="s">
         <v>88</v>
       </c>
@@ -3225,8 +3465,11 @@
       <c r="N111" s="38" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="112" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="W111" s="38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B112" s="45">
         <v>1</v>
       </c>
@@ -3248,6 +3491,12 @@
       </c>
       <c r="P112" s="56"/>
       <c r="Q112" s="47"/>
+      <c r="W112" s="45">
+        <v>1</v>
+      </c>
+      <c r="X112" s="45">
+        <v>2</v>
+      </c>
     </row>
     <row r="113" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B113" s="45">
@@ -3265,6 +3514,10 @@
       <c r="O113" s="56"/>
       <c r="P113" s="56"/>
       <c r="Q113" s="47"/>
+      <c r="W113" s="45">
+        <v>2</v>
+      </c>
+      <c r="X113" s="45"/>
     </row>
     <row r="114" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B114" s="45">
@@ -3282,6 +3535,10 @@
       <c r="O114" s="56"/>
       <c r="P114" s="56"/>
       <c r="Q114" s="47"/>
+      <c r="W114" s="45">
+        <v>3</v>
+      </c>
+      <c r="X114" s="45"/>
     </row>
     <row r="115" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B115" s="45">
@@ -3299,6 +3556,10 @@
       <c r="O115" s="56"/>
       <c r="P115" s="56"/>
       <c r="Q115" s="47"/>
+      <c r="W115" s="45">
+        <v>4</v>
+      </c>
+      <c r="X115" s="45"/>
     </row>
     <row r="117" spans="2:34" x14ac:dyDescent="0.25">
       <c r="G117" s="38" t="s">
@@ -3312,6 +3573,9 @@
       </c>
       <c r="O117" s="57" t="s">
         <v>104</v>
+      </c>
+      <c r="W117" s="38" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="118" spans="2:34" x14ac:dyDescent="0.25">
@@ -4489,6 +4753,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C15:AC15"/>
+    <mergeCell ref="B13:AC13"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="AA7:AC7"/>
+    <mergeCell ref="AA8:AC8"/>
+    <mergeCell ref="AA9:AC9"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="B10:AC10"/>
@@ -4504,13 +4775,6 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C15:AC15"/>
-    <mergeCell ref="B13:AC13"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="AA7:AC7"/>
-    <mergeCell ref="AA8:AC8"/>
-    <mergeCell ref="AA9:AC9"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
